--- a/plateau_table_equityV.xlsx
+++ b/plateau_table_equityV.xlsx
@@ -15,102 +15,228 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
-  <si>
-    <t>SMA</t>
-  </si>
-  <si>
-    <t>CAGR</t>
-  </si>
-  <si>
-    <t>MaxDD</t>
-  </si>
-  <si>
-    <t>Calmar</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+  <si>
+    <t>SMA 週期</t>
+  </si>
+  <si>
+    <t>年化報酬率 (CAGR)</t>
+  </si>
+  <si>
+    <t>最大回撤 (MaxDD)</t>
+  </si>
+  <si>
+    <t>Calmar Ratio</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>**303 (選定)**</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>27.99%</t>
+  </si>
+  <si>
+    <t>28.83%</t>
+  </si>
+  <si>
+    <t>26.31%</t>
   </si>
   <si>
     <t>19.78%</t>
   </si>
   <si>
-    <t>27.05%</t>
-  </si>
-  <si>
     <t>31.98%</t>
   </si>
   <si>
-    <t>27.90%</t>
-  </si>
-  <si>
     <t>29.93%</t>
   </si>
   <si>
+    <t>31.43%</t>
+  </si>
+  <si>
+    <t>23.75%</t>
+  </si>
+  <si>
+    <t>27.24%</t>
+  </si>
+  <si>
+    <t>-25.62%</t>
+  </si>
+  <si>
+    <t>-17.29%</t>
+  </si>
+  <si>
+    <t>-22.62%</t>
+  </si>
+  <si>
     <t>-30.02%</t>
   </si>
   <si>
-    <t>-32.42%</t>
-  </si>
-  <si>
     <t>-10.94%</t>
   </si>
   <si>
-    <t>-27.55%</t>
-  </si>
-  <si>
     <t>-23.88%</t>
   </si>
   <si>
+    <t>-16.59%</t>
+  </si>
+  <si>
+    <t>-30.13%</t>
+  </si>
+  <si>
+    <t>-32.61%</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>1.67</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
     <t>0.66</t>
   </si>
   <si>
-    <t>0.83</t>
-  </si>
-  <si>
     <t>2.92</t>
   </si>
   <si>
-    <t>1.01</t>
-  </si>
-  <si>
     <t>1.25</t>
   </si>
   <si>
-    <t>ROC</t>
+    <t>1.89</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>ROC 週期</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>**14 (選定)**</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>30.04%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>31.94%</t>
   </si>
   <si>
     <t>31.57%</t>
   </si>
   <si>
-    <t>29.75%</t>
-  </si>
-  <si>
-    <t>32.86%</t>
-  </si>
-  <si>
     <t>32.83%</t>
   </si>
   <si>
+    <t>31.38%</t>
+  </si>
+  <si>
+    <t>30.27%</t>
+  </si>
+  <si>
+    <t>31.85%</t>
+  </si>
+  <si>
+    <t>-17.68%</t>
+  </si>
+  <si>
+    <t>-13.09%</t>
+  </si>
+  <si>
+    <t>-12.23%</t>
+  </si>
+  <si>
     <t>-12.20%</t>
   </si>
   <si>
-    <t>-13.53%</t>
-  </si>
-  <si>
-    <t>-14.31%</t>
-  </si>
-  <si>
     <t>-14.54%</t>
   </si>
   <si>
+    <t>-14.27%</t>
+  </si>
+  <si>
+    <t>-11.64%</t>
+  </si>
+  <si>
+    <t>-14.99%</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>2.07</t>
+  </si>
+  <si>
+    <t>2.61</t>
+  </si>
+  <si>
     <t>2.59</t>
   </si>
   <si>
+    <t>2.26</t>
+  </si>
+  <si>
     <t>2.20</t>
   </si>
   <si>
-    <t>2.30</t>
-  </si>
-  <si>
-    <t>2.26</t>
+    <t>2.60</t>
+  </si>
+  <si>
+    <t>2.12</t>
   </si>
 </sst>
 </file>
@@ -442,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -460,73 +586,129 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2">
-        <v>301</v>
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>302</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>303</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>304</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>305</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -536,12 +718,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -554,73 +736,129 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3">
-        <v>13</v>
+      <c r="A3" t="s">
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4">
-        <v>14</v>
+      <c r="A4" t="s">
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5">
-        <v>15</v>
+      <c r="A5" t="s">
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
